--- a/companies/alder-ridge/source-files/Shared/Finance/Corporate Development/Active analyses/IC model inputs - 7.5 controller tie.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Corporate Development/Active analyses/IC model inputs - 7.5 controller tie.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QoE and Working Capital'!$A$4:$M$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QoE and Working Capital'!$A$4:$M$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Valuation'!$A$4:$M$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Transaction Models'!$A$4:$M$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Carveout and Integration'!$A$4:$M$85</definedName>
@@ -646,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -778,11 +778,11 @@
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>Proposed EBITDA adjustment</t>
+          <t>Seller proposed EBITDA adjustment</t>
         </is>
       </c>
       <c r="H5" s="46" t="n">
-        <v>240000</v>
+        <v>300000</v>
       </c>
       <c r="I5" s="27" t="inlineStr"/>
       <c r="J5" s="27" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K5" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Seller QoE schedule</t>
         </is>
       </c>
       <c r="L5" s="47" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
@@ -835,23 +835,21 @@
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>Diligence conclusion</t>
-        </is>
-      </c>
-      <c r="H6" s="46" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
+          <t>LTM compensation recorded</t>
+        </is>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>520000</v>
+      </c>
+      <c r="I6" s="27" t="inlineStr"/>
       <c r="J6" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K6" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Target payroll export</t>
         </is>
       </c>
       <c r="L6" s="47" t="inlineStr">
@@ -874,7 +872,7 @@
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
@@ -894,23 +892,21 @@
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
-          <t>Evidence basis</t>
-        </is>
-      </c>
-      <c r="H7" s="46" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
-          <t>Contract and payroll support</t>
-        </is>
-      </c>
+          <t>Market replacement compensation</t>
+        </is>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>280000</v>
+      </c>
+      <c r="I7" s="27" t="inlineStr"/>
       <c r="J7" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K7" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Compensation diligence benchmark</t>
         </is>
       </c>
       <c r="L7" s="47" t="inlineStr">
@@ -933,7 +929,7 @@
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
@@ -953,11 +949,11 @@
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t>Proposed EBITDA adjustment</t>
+          <t>Seller proposed EBITDA adjustment</t>
         </is>
       </c>
       <c r="H8" s="46" t="n">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="I8" s="27" t="inlineStr"/>
       <c r="J8" s="27" t="inlineStr">
@@ -967,7 +963,7 @@
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Seller QoE schedule</t>
         </is>
       </c>
       <c r="L8" s="47" t="inlineStr">
@@ -990,7 +986,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
@@ -1010,23 +1006,21 @@
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
-          <t>Diligence conclusion</t>
-        </is>
-      </c>
-      <c r="H9" s="46" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
+          <t>Settlement expense recorded</t>
+        </is>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>235000</v>
+      </c>
+      <c r="I9" s="27" t="inlineStr"/>
       <c r="J9" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K9" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Executed settlement and ledger detail</t>
         </is>
       </c>
       <c r="L9" s="47" t="inlineStr">
@@ -1049,7 +1043,7 @@
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
@@ -1069,23 +1063,21 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>Evidence basis</t>
-        </is>
-      </c>
-      <c r="H10" s="46" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
-        <is>
-          <t>Executed settlement</t>
-        </is>
-      </c>
+          <t>Insurance reimbursement recorded against expense</t>
+        </is>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I10" s="27" t="inlineStr"/>
       <c r="J10" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K10" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Target general ledger detail</t>
         </is>
       </c>
       <c r="L10" s="47" t="inlineStr">
@@ -1108,7 +1100,7 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
@@ -1128,11 +1120,11 @@
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>Proposed EBITDA adjustment</t>
+          <t>Seller proposed EBITDA adjustment</t>
         </is>
       </c>
       <c r="H11" s="46" t="n">
-        <v>-155000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="27" t="inlineStr"/>
       <c r="J11" s="27" t="inlineStr">
@@ -1142,7 +1134,7 @@
       </c>
       <c r="K11" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Seller QoE schedule</t>
         </is>
       </c>
       <c r="L11" s="47" t="inlineStr">
@@ -1165,7 +1157,7 @@
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
@@ -1185,23 +1177,21 @@
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>Diligence conclusion</t>
-        </is>
-      </c>
-      <c r="H12" s="46" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
+          <t>Annual market replacement compensation</t>
+        </is>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>186</v>
+      </c>
+      <c r="I12" s="27" t="inlineStr"/>
       <c r="J12" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K12" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Executed search engagement terms</t>
         </is>
       </c>
       <c r="L12" s="47" t="inlineStr">
@@ -1224,7 +1214,7 @@
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
@@ -1244,23 +1234,21 @@
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>Evidence basis</t>
-        </is>
-      </c>
-      <c r="H13" s="46" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>Required replacement cost</t>
-        </is>
-      </c>
+          <t>Vacant months in LTM</t>
+        </is>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="27" t="inlineStr"/>
       <c r="J13" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>count</t>
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Target payroll export</t>
         </is>
       </c>
       <c r="L13" s="47" t="inlineStr">
@@ -1283,7 +1271,7 @@
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
@@ -1303,7 +1291,7 @@
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>Proposed EBITDA adjustment</t>
+          <t>Seller proposed EBITDA adjustment</t>
         </is>
       </c>
       <c r="H14" s="46" t="n">
@@ -1317,7 +1305,7 @@
       </c>
       <c r="K14" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Seller QoE schedule</t>
         </is>
       </c>
       <c r="L14" s="47" t="inlineStr">
@@ -1340,7 +1328,7 @@
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
@@ -1360,23 +1348,21 @@
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>Diligence conclusion</t>
-        </is>
-      </c>
-      <c r="H15" s="46" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
+          <t>Savings realized through cutoff</t>
+        </is>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr"/>
       <c r="J15" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K15" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Procurement diligence tracker</t>
         </is>
       </c>
       <c r="L15" s="47" t="inlineStr">
@@ -1399,7 +1385,7 @@
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -1419,13 +1405,13 @@
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>Evidence basis</t>
+          <t>Execution basis</t>
         </is>
       </c>
       <c r="H16" s="46" t="inlineStr"/>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>Buyer-specific future synergy</t>
+          <t>Post-close buyer scale; no contract</t>
         </is>
       </c>
       <c r="J16" s="27" t="inlineStr">
@@ -1435,7 +1421,7 @@
       </c>
       <c r="K16" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Procurement diligence tracker</t>
         </is>
       </c>
       <c r="L16" s="47" t="inlineStr">
@@ -1458,7 +1444,7 @@
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
@@ -1478,7 +1464,7 @@
       </c>
       <c r="G17" s="27" t="inlineStr">
         <is>
-          <t>Proposed EBITDA adjustment</t>
+          <t>Seller proposed EBITDA adjustment</t>
         </is>
       </c>
       <c r="H17" s="46" t="n">
@@ -1492,7 +1478,7 @@
       </c>
       <c r="K17" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Seller QoE schedule</t>
         </is>
       </c>
       <c r="L17" s="47" t="inlineStr">
@@ -1515,7 +1501,7 @@
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
@@ -1535,23 +1521,21 @@
       </c>
       <c r="G18" s="27" t="inlineStr">
         <is>
-          <t>Diligence conclusion</t>
-        </is>
-      </c>
-      <c r="H18" s="46" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
+          <t>Executed annual rent reduction</t>
+        </is>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr"/>
       <c r="J18" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K18" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Facility diligence tracker</t>
         </is>
       </c>
       <c r="L18" s="47" t="inlineStr">
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustment register</t>
+          <t>QoE adjustment evidence</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
@@ -1594,13 +1578,13 @@
       </c>
       <c r="G19" s="27" t="inlineStr">
         <is>
-          <t>Evidence basis</t>
+          <t>Execution basis</t>
         </is>
       </c>
       <c r="H19" s="46" t="inlineStr"/>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>No executed lease action</t>
+          <t>Lease unsigned; target remains obligated</t>
         </is>
       </c>
       <c r="J19" s="27" t="inlineStr">
@@ -1610,7 +1594,7 @@
       </c>
       <c r="K19" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Facility diligence tracker</t>
         </is>
       </c>
       <c r="L19" s="47" t="inlineStr">
@@ -1965,27 +1949,27 @@
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>DEV-00142</t>
+          <t>DEV-00058</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>BluePeak normalized working-capital peg</t>
+          <t>Redwood Controls quality-of-earnings normalization</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>Estimated closing NWC</t>
+          <t>IC valuation assumptions</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>BluePeak</t>
+          <t>Redwood Controls</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="F26" s="27" t="inlineStr">
@@ -1995,21 +1979,21 @@
       </c>
       <c r="G26" s="27" t="inlineStr">
         <is>
-          <t>Trade AR</t>
+          <t>Working entry multiple</t>
         </is>
       </c>
       <c r="H26" s="46" t="n">
-        <v>4100000</v>
+        <v>7.5</v>
       </c>
       <c r="I26" s="27" t="inlineStr"/>
       <c r="J26" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="K26" s="27" t="inlineStr">
         <is>
-          <t>Finance operating schedule</t>
+          <t>Controller-tied IC case book</t>
         </is>
       </c>
       <c r="L26" s="47" t="inlineStr">
@@ -2022,7 +2006,7 @@
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>DEV-00143</t>
+          <t>DEV-00142</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
@@ -2032,7 +2016,7 @@
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>Estimated closing NWC</t>
+          <t>Purchase agreement</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
@@ -2042,7 +2026,7 @@
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Signing</t>
         </is>
       </c>
       <c r="F27" s="27" t="inlineStr">
@@ -2052,11 +2036,11 @@
       </c>
       <c r="G27" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Peg collar</t>
         </is>
       </c>
       <c r="H27" s="46" t="n">
-        <v>1420000</v>
+        <v>250000</v>
       </c>
       <c r="I27" s="27" t="inlineStr"/>
       <c r="J27" s="27" t="inlineStr">
@@ -2079,7 +2063,7 @@
     <row r="28">
       <c r="A28" s="36" t="inlineStr">
         <is>
-          <t>DEV-00144</t>
+          <t>DEV-00143</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
@@ -2089,7 +2073,7 @@
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>Estimated closing NWC</t>
+          <t>Purchase agreement</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -2099,7 +2083,7 @@
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Signing</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
@@ -2109,16 +2093,16 @@
       </c>
       <c r="G28" s="27" t="inlineStr">
         <is>
-          <t>Trade AP</t>
+          <t>Shortfall adjustment rate</t>
         </is>
       </c>
       <c r="H28" s="46" t="n">
-        <v>2490000</v>
+        <v>1</v>
       </c>
       <c r="I28" s="27" t="inlineStr"/>
       <c r="J28" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD per USD</t>
         </is>
       </c>
       <c r="K28" s="27" t="inlineStr">
@@ -2136,7 +2120,7 @@
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
         <is>
-          <t>DEV-00145</t>
+          <t>DEV-00144</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
@@ -2146,17 +2130,17 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>Estimated closing NWC</t>
+          <t>Diligence peg treatment</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>BluePeak</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
@@ -2166,16 +2150,18 @@
       </c>
       <c r="G29" s="27" t="inlineStr">
         <is>
-          <t>Accrued operating liabilities</t>
-        </is>
-      </c>
-      <c r="H29" s="46" t="n">
-        <v>520</v>
-      </c>
-      <c r="I29" s="27" t="inlineStr"/>
+          <t>Peg treatment</t>
+        </is>
+      </c>
+      <c r="H29" s="46" t="inlineStr"/>
+      <c r="I29" s="27" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
       <c r="J29" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K29" s="27" t="inlineStr">
@@ -2193,7 +2179,7 @@
     <row r="30">
       <c r="A30" s="36" t="inlineStr">
         <is>
-          <t>DEV-00146</t>
+          <t>DEV-00145</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
@@ -2203,17 +2189,17 @@
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>Estimated closing NWC</t>
+          <t>Diligence peg treatment</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>BluePeak</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
@@ -2223,16 +2209,18 @@
       </c>
       <c r="G30" s="27" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="H30" s="46" t="n">
-        <v>360000</v>
-      </c>
-      <c r="I30" s="27" t="inlineStr"/>
+          <t>Peg treatment</t>
+        </is>
+      </c>
+      <c r="H30" s="46" t="inlineStr"/>
+      <c r="I30" s="27" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
       <c r="J30" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K30" s="27" t="inlineStr">
@@ -2250,7 +2238,7 @@
     <row r="31">
       <c r="A31" s="36" t="inlineStr">
         <is>
-          <t>DEV-00147</t>
+          <t>DEV-00146</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
@@ -2260,17 +2248,17 @@
       </c>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>Purchase agreement</t>
+          <t>Closing eligibility condition</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>BluePeak</t>
+          <t>Disputed change-order receivable</t>
         </is>
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
-          <t>Signing</t>
+          <t>Estimated closing</t>
         </is>
       </c>
       <c r="F31" s="27" t="inlineStr">
@@ -2280,16 +2268,18 @@
       </c>
       <c r="G31" s="27" t="inlineStr">
         <is>
-          <t>Peg collar</t>
-        </is>
-      </c>
-      <c r="H31" s="46" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I31" s="27" t="inlineStr"/>
+          <t>Required support</t>
+        </is>
+      </c>
+      <c r="H31" s="46" t="inlineStr"/>
+      <c r="I31" s="27" t="inlineStr">
+        <is>
+          <t>signed customer acceptance</t>
+        </is>
+      </c>
       <c r="J31" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K31" s="27" t="inlineStr">
@@ -2307,27 +2297,27 @@
     <row r="32">
       <c r="A32" s="36" t="inlineStr">
         <is>
-          <t>DEV-00409</t>
+          <t>DEV-00147</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Create the Pioneer QoE and purchase-price bridge</t>
+          <t>BluePeak normalized working-capital peg</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>Target reported results</t>
+          <t>Closing eligibility condition</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>Pioneer HVAC</t>
+          <t>Disputed change-order receivable</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>LTM 2026-06-30</t>
+          <t>Estimated closing</t>
         </is>
       </c>
       <c r="F32" s="27" t="inlineStr">
@@ -2337,16 +2327,18 @@
       </c>
       <c r="G32" s="27" t="inlineStr">
         <is>
-          <t>Reported EBITDA</t>
-        </is>
-      </c>
-      <c r="H32" s="46" t="n">
-        <v>4860000</v>
-      </c>
-      <c r="I32" s="27" t="inlineStr"/>
+          <t>Eligibility with support</t>
+        </is>
+      </c>
+      <c r="H32" s="46" t="inlineStr"/>
+      <c r="I32" s="27" t="inlineStr">
+        <is>
+          <t>Included in operating NWC</t>
+        </is>
+      </c>
       <c r="J32" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K32" s="27" t="inlineStr">
@@ -2364,7 +2356,7 @@
     <row r="33">
       <c r="A33" s="36" t="inlineStr">
         <is>
-          <t>DEV-00410</t>
+          <t>DEV-00409</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
@@ -2374,12 +2366,12 @@
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>QoE adjustments</t>
+          <t>Target reported results</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
-          <t>Owner compensation normalization</t>
+          <t>Pioneer HVAC</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
@@ -2394,11 +2386,11 @@
       </c>
       <c r="G33" s="27" t="inlineStr">
         <is>
-          <t>EBITDA adjustment</t>
+          <t>Reported EBITDA</t>
         </is>
       </c>
       <c r="H33" s="46" t="n">
-        <v>420000</v>
+        <v>4860000</v>
       </c>
       <c r="I33" s="27" t="inlineStr"/>
       <c r="J33" s="27" t="inlineStr">
@@ -2421,7 +2413,7 @@
     <row r="34">
       <c r="A34" s="36" t="inlineStr">
         <is>
-          <t>DEV-00411</t>
+          <t>DEV-00410</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
@@ -2451,16 +2443,16 @@
       </c>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>Include in QoE</t>
+          <t>EBITDA adjustment</t>
         </is>
       </c>
       <c r="H34" s="46" t="n">
-        <v>1</v>
+        <v>420000</v>
       </c>
       <c r="I34" s="27" t="inlineStr"/>
       <c r="J34" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K34" s="27" t="inlineStr">
@@ -2478,7 +2470,7 @@
     <row r="35">
       <c r="A35" s="36" t="inlineStr">
         <is>
-          <t>DEV-00412</t>
+          <t>DEV-00411</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
@@ -2508,18 +2500,16 @@
       </c>
       <c r="G35" s="27" t="inlineStr">
         <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="H35" s="46" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
-        <is>
-          <t>Recurring normalization</t>
-        </is>
-      </c>
+          <t>Include in QoE</t>
+        </is>
+      </c>
+      <c r="H35" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="27" t="inlineStr"/>
       <c r="J35" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K35" s="27" t="inlineStr">
@@ -2537,7 +2527,7 @@
     <row r="36">
       <c r="A36" s="36" t="inlineStr">
         <is>
-          <t>DEV-00413</t>
+          <t>DEV-00412</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
@@ -2552,7 +2542,7 @@
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>Uninsured storm loss</t>
+          <t>Owner compensation normalization</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
@@ -2567,16 +2557,18 @@
       </c>
       <c r="G36" s="27" t="inlineStr">
         <is>
-          <t>EBITDA adjustment</t>
-        </is>
-      </c>
-      <c r="H36" s="46" t="n">
-        <v>285000</v>
-      </c>
-      <c r="I36" s="27" t="inlineStr"/>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="H36" s="46" t="inlineStr"/>
+      <c r="I36" s="27" t="inlineStr">
+        <is>
+          <t>Recurring normalization</t>
+        </is>
+      </c>
       <c r="J36" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K36" s="27" t="inlineStr">
@@ -2594,7 +2586,7 @@
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
         <is>
-          <t>DEV-00414</t>
+          <t>DEV-00413</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
@@ -2624,16 +2616,16 @@
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>Include in QoE</t>
+          <t>EBITDA adjustment</t>
         </is>
       </c>
       <c r="H37" s="46" t="n">
-        <v>1</v>
+        <v>285000</v>
       </c>
       <c r="I37" s="27" t="inlineStr"/>
       <c r="J37" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K37" s="27" t="inlineStr">
@@ -2651,7 +2643,7 @@
     <row r="38">
       <c r="A38" s="36" t="inlineStr">
         <is>
-          <t>DEV-00415</t>
+          <t>DEV-00414</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
@@ -2681,18 +2673,16 @@
       </c>
       <c r="G38" s="27" t="inlineStr">
         <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="H38" s="46" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr">
-        <is>
-          <t>Nonrecurring</t>
-        </is>
-      </c>
+          <t>Include in QoE</t>
+        </is>
+      </c>
+      <c r="H38" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="27" t="inlineStr"/>
       <c r="J38" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K38" s="27" t="inlineStr">
@@ -2710,7 +2700,7 @@
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>DEV-00416</t>
+          <t>DEV-00415</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
@@ -2725,7 +2715,7 @@
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>Run-rate sales hires</t>
+          <t>Uninsured storm loss</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
@@ -2740,16 +2730,18 @@
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>EBITDA adjustment</t>
-        </is>
-      </c>
-      <c r="H39" s="46" t="n">
-        <v>-360</v>
-      </c>
-      <c r="I39" s="27" t="inlineStr"/>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="H39" s="46" t="inlineStr"/>
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>Nonrecurring</t>
+        </is>
+      </c>
       <c r="J39" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K39" s="27" t="inlineStr">
@@ -2767,7 +2759,7 @@
     <row r="40">
       <c r="A40" s="36" t="inlineStr">
         <is>
-          <t>DEV-00417</t>
+          <t>DEV-00416</t>
         </is>
       </c>
       <c r="B40" s="27" t="inlineStr">
@@ -2797,16 +2789,16 @@
       </c>
       <c r="G40" s="27" t="inlineStr">
         <is>
-          <t>Include in QoE</t>
+          <t>EBITDA adjustment</t>
         </is>
       </c>
       <c r="H40" s="46" t="n">
-        <v>1</v>
+        <v>-360</v>
       </c>
       <c r="I40" s="27" t="inlineStr"/>
       <c r="J40" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K40" s="27" t="inlineStr">
@@ -2824,7 +2816,7 @@
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
         <is>
-          <t>DEV-00418</t>
+          <t>DEV-00417</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
@@ -2854,18 +2846,16 @@
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="H41" s="46" t="inlineStr"/>
-      <c r="I41" s="27" t="inlineStr">
-        <is>
-          <t>Missing recurring cost</t>
-        </is>
-      </c>
+          <t>Include in QoE</t>
+        </is>
+      </c>
+      <c r="H41" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="27" t="inlineStr"/>
       <c r="J41" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K41" s="27" t="inlineStr">
@@ -2883,7 +2873,7 @@
     <row r="42">
       <c r="A42" s="36" t="inlineStr">
         <is>
-          <t>DEV-00419</t>
+          <t>DEV-00418</t>
         </is>
       </c>
       <c r="B42" s="27" t="inlineStr">
@@ -2898,7 +2888,7 @@
       </c>
       <c r="D42" s="27" t="inlineStr">
         <is>
-          <t>Proposed procurement synergy</t>
+          <t>Run-rate sales hires</t>
         </is>
       </c>
       <c r="E42" s="27" t="inlineStr">
@@ -2913,16 +2903,18 @@
       </c>
       <c r="G42" s="27" t="inlineStr">
         <is>
-          <t>EBITDA adjustment</t>
-        </is>
-      </c>
-      <c r="H42" s="46" t="n">
-        <v>610000</v>
-      </c>
-      <c r="I42" s="27" t="inlineStr"/>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="H42" s="46" t="inlineStr"/>
+      <c r="I42" s="27" t="inlineStr">
+        <is>
+          <t>Missing recurring cost</t>
+        </is>
+      </c>
       <c r="J42" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K42" s="27" t="inlineStr">
@@ -2940,7 +2932,7 @@
     <row r="43">
       <c r="A43" s="36" t="inlineStr">
         <is>
-          <t>DEV-00420</t>
+          <t>DEV-00419</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
@@ -2970,16 +2962,16 @@
       </c>
       <c r="G43" s="27" t="inlineStr">
         <is>
-          <t>Include in QoE</t>
+          <t>EBITDA adjustment</t>
         </is>
       </c>
       <c r="H43" s="46" t="n">
-        <v>0</v>
+        <v>610000</v>
       </c>
       <c r="I43" s="27" t="inlineStr"/>
       <c r="J43" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K43" s="27" t="inlineStr">
@@ -2997,7 +2989,7 @@
     <row r="44">
       <c r="A44" s="36" t="inlineStr">
         <is>
-          <t>DEV-00421</t>
+          <t>DEV-00420</t>
         </is>
       </c>
       <c r="B44" s="27" t="inlineStr">
@@ -3027,18 +3019,16 @@
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="H44" s="46" t="inlineStr"/>
-      <c r="I44" s="27" t="inlineStr">
-        <is>
-          <t>Buyer synergy</t>
-        </is>
-      </c>
+          <t>Include in QoE</t>
+        </is>
+      </c>
+      <c r="H44" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="27" t="inlineStr"/>
       <c r="J44" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K44" s="27" t="inlineStr">
@@ -3056,7 +3046,7 @@
     <row r="45">
       <c r="A45" s="36" t="inlineStr">
         <is>
-          <t>DEV-00422</t>
+          <t>DEV-00421</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
@@ -3071,7 +3061,7 @@
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>Discontinued branch losses</t>
+          <t>Proposed procurement synergy</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
@@ -3086,16 +3076,18 @@
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>EBITDA adjustment</t>
-        </is>
-      </c>
-      <c r="H45" s="46" t="n">
-        <v>175000</v>
-      </c>
-      <c r="I45" s="27" t="inlineStr"/>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="H45" s="46" t="inlineStr"/>
+      <c r="I45" s="27" t="inlineStr">
+        <is>
+          <t>Buyer synergy</t>
+        </is>
+      </c>
       <c r="J45" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K45" s="27" t="inlineStr">
@@ -3113,7 +3105,7 @@
     <row r="46">
       <c r="A46" s="36" t="inlineStr">
         <is>
-          <t>DEV-00423</t>
+          <t>DEV-00422</t>
         </is>
       </c>
       <c r="B46" s="27" t="inlineStr">
@@ -3143,16 +3135,16 @@
       </c>
       <c r="G46" s="27" t="inlineStr">
         <is>
-          <t>Include in QoE</t>
+          <t>EBITDA adjustment</t>
         </is>
       </c>
       <c r="H46" s="46" t="n">
-        <v>1</v>
+        <v>175000</v>
       </c>
       <c r="I46" s="27" t="inlineStr"/>
       <c r="J46" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K46" s="27" t="inlineStr">
@@ -3170,7 +3162,7 @@
     <row r="47">
       <c r="A47" s="36" t="inlineStr">
         <is>
-          <t>DEV-00424</t>
+          <t>DEV-00423</t>
         </is>
       </c>
       <c r="B47" s="27" t="inlineStr">
@@ -3200,18 +3192,16 @@
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="H47" s="46" t="inlineStr"/>
-      <c r="I47" s="27" t="inlineStr">
-        <is>
-          <t>Disposed before close</t>
-        </is>
-      </c>
+          <t>Include in QoE</t>
+        </is>
+      </c>
+      <c r="H47" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="27" t="inlineStr"/>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K47" s="27" t="inlineStr">
@@ -3229,7 +3219,7 @@
     <row r="48">
       <c r="A48" s="36" t="inlineStr">
         <is>
-          <t>DEV-00425</t>
+          <t>DEV-00424</t>
         </is>
       </c>
       <c r="B48" s="27" t="inlineStr">
@@ -3244,7 +3234,7 @@
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
-          <t>Banker revenue uplift</t>
+          <t>Discontinued branch losses</t>
         </is>
       </c>
       <c r="E48" s="27" t="inlineStr">
@@ -3259,16 +3249,18 @@
       </c>
       <c r="G48" s="27" t="inlineStr">
         <is>
-          <t>EBITDA adjustment</t>
-        </is>
-      </c>
-      <c r="H48" s="46" t="n">
-        <v>540000</v>
-      </c>
-      <c r="I48" s="27" t="inlineStr"/>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="H48" s="46" t="inlineStr"/>
+      <c r="I48" s="27" t="inlineStr">
+        <is>
+          <t>Disposed before close</t>
+        </is>
+      </c>
       <c r="J48" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K48" s="27" t="inlineStr">
@@ -3286,7 +3278,7 @@
     <row r="49">
       <c r="A49" s="36" t="inlineStr">
         <is>
-          <t>DEV-00426</t>
+          <t>DEV-00425</t>
         </is>
       </c>
       <c r="B49" s="27" t="inlineStr">
@@ -3316,16 +3308,16 @@
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>Include in QoE</t>
+          <t>EBITDA adjustment</t>
         </is>
       </c>
       <c r="H49" s="46" t="n">
-        <v>0</v>
+        <v>540000</v>
       </c>
       <c r="I49" s="27" t="inlineStr"/>
       <c r="J49" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K49" s="27" t="inlineStr">
@@ -3343,7 +3335,7 @@
     <row r="50">
       <c r="A50" s="36" t="inlineStr">
         <is>
-          <t>DEV-00427</t>
+          <t>DEV-00426</t>
         </is>
       </c>
       <c r="B50" s="27" t="inlineStr">
@@ -3373,18 +3365,16 @@
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="H50" s="46" t="inlineStr"/>
-      <c r="I50" s="27" t="inlineStr">
-        <is>
-          <t>Unsupported forecast</t>
-        </is>
-      </c>
+          <t>Include in QoE</t>
+        </is>
+      </c>
+      <c r="H50" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="27" t="inlineStr"/>
       <c r="J50" s="27" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K50" s="27" t="inlineStr">
@@ -3402,7 +3392,7 @@
     <row r="51">
       <c r="A51" s="36" t="inlineStr">
         <is>
-          <t>DEV-00428</t>
+          <t>DEV-00427</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
@@ -3412,17 +3402,17 @@
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>Target monthly working capital</t>
+          <t>QoE adjustments</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>Pioneer HVAC</t>
+          <t>Banker revenue uplift</t>
         </is>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>LTM 2026-06-30</t>
         </is>
       </c>
       <c r="F51" s="27" t="inlineStr">
@@ -3432,16 +3422,18 @@
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="H51" s="46" t="n">
-        <v>6200</v>
-      </c>
-      <c r="I51" s="27" t="inlineStr"/>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="H51" s="46" t="inlineStr"/>
+      <c r="I51" s="27" t="inlineStr">
+        <is>
+          <t>Unsupported forecast</t>
+        </is>
+      </c>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K51" s="27" t="inlineStr">
@@ -3459,7 +3451,7 @@
     <row r="52">
       <c r="A52" s="36" t="inlineStr">
         <is>
-          <t>DEV-00429</t>
+          <t>DEV-00428</t>
         </is>
       </c>
       <c r="B52" s="27" t="inlineStr">
@@ -3489,16 +3481,16 @@
       </c>
       <c r="G52" s="27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H52" s="46" t="n">
-        <v>2050000</v>
+        <v>6200</v>
       </c>
       <c r="I52" s="27" t="inlineStr"/>
       <c r="J52" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K52" s="27" t="inlineStr">
@@ -3516,7 +3508,7 @@
     <row r="53">
       <c r="A53" s="36" t="inlineStr">
         <is>
-          <t>DEV-00430</t>
+          <t>DEV-00429</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
@@ -3546,11 +3538,11 @@
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="H53" s="46" t="n">
-        <v>2420000</v>
+        <v>2050000</v>
       </c>
       <c r="I53" s="27" t="inlineStr"/>
       <c r="J53" s="27" t="inlineStr">
@@ -3573,7 +3565,7 @@
     <row r="54">
       <c r="A54" s="36" t="inlineStr">
         <is>
-          <t>DEV-00431</t>
+          <t>DEV-00430</t>
         </is>
       </c>
       <c r="B54" s="27" t="inlineStr">
@@ -3603,11 +3595,11 @@
       </c>
       <c r="G54" s="27" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="H54" s="46" t="n">
-        <v>1130000</v>
+        <v>2420000</v>
       </c>
       <c r="I54" s="27" t="inlineStr"/>
       <c r="J54" s="27" t="inlineStr">
@@ -3630,7 +3622,7 @@
     <row r="55">
       <c r="A55" s="36" t="inlineStr">
         <is>
-          <t>DEV-00432</t>
+          <t>DEV-00431</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
@@ -3650,7 +3642,7 @@
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F55" s="27" t="inlineStr">
@@ -3660,16 +3652,16 @@
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="H55" s="46" t="n">
-        <v>6480</v>
+        <v>1130000</v>
       </c>
       <c r="I55" s="27" t="inlineStr"/>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K55" s="27" t="inlineStr">
@@ -3687,7 +3679,7 @@
     <row r="56">
       <c r="A56" s="36" t="inlineStr">
         <is>
-          <t>DEV-00433</t>
+          <t>DEV-00432</t>
         </is>
       </c>
       <c r="B56" s="27" t="inlineStr">
@@ -3717,16 +3709,16 @@
       </c>
       <c r="G56" s="27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H56" s="46" t="n">
-        <v>2210000</v>
+        <v>6480</v>
       </c>
       <c r="I56" s="27" t="inlineStr"/>
       <c r="J56" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K56" s="27" t="inlineStr">
@@ -3744,7 +3736,7 @@
     <row r="57">
       <c r="A57" s="36" t="inlineStr">
         <is>
-          <t>DEV-00434</t>
+          <t>DEV-00433</t>
         </is>
       </c>
       <c r="B57" s="27" t="inlineStr">
@@ -3774,11 +3766,11 @@
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="H57" s="46" t="n">
-        <v>2510000</v>
+        <v>2210000</v>
       </c>
       <c r="I57" s="27" t="inlineStr"/>
       <c r="J57" s="27" t="inlineStr">
@@ -3801,7 +3793,7 @@
     <row r="58">
       <c r="A58" s="36" t="inlineStr">
         <is>
-          <t>DEV-00435</t>
+          <t>DEV-00434</t>
         </is>
       </c>
       <c r="B58" s="27" t="inlineStr">
@@ -3831,11 +3823,11 @@
       </c>
       <c r="G58" s="27" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="H58" s="46" t="n">
-        <v>1180000</v>
+        <v>2510000</v>
       </c>
       <c r="I58" s="27" t="inlineStr"/>
       <c r="J58" s="27" t="inlineStr">
@@ -3858,7 +3850,7 @@
     <row r="59">
       <c r="A59" s="36" t="inlineStr">
         <is>
-          <t>DEV-00436</t>
+          <t>DEV-00435</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
@@ -3878,7 +3870,7 @@
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F59" s="27" t="inlineStr">
@@ -3888,16 +3880,16 @@
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="H59" s="46" t="n">
-        <v>6850</v>
+        <v>1180000</v>
       </c>
       <c r="I59" s="27" t="inlineStr"/>
       <c r="J59" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K59" s="27" t="inlineStr">
@@ -3915,7 +3907,7 @@
     <row r="60">
       <c r="A60" s="36" t="inlineStr">
         <is>
-          <t>DEV-00437</t>
+          <t>DEV-00436</t>
         </is>
       </c>
       <c r="B60" s="27" t="inlineStr">
@@ -3945,16 +3937,16 @@
       </c>
       <c r="G60" s="27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H60" s="46" t="n">
-        <v>2380000</v>
+        <v>6850</v>
       </c>
       <c r="I60" s="27" t="inlineStr"/>
       <c r="J60" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K60" s="27" t="inlineStr">
@@ -3972,7 +3964,7 @@
     <row r="61">
       <c r="A61" s="36" t="inlineStr">
         <is>
-          <t>DEV-00438</t>
+          <t>DEV-00437</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
@@ -4002,11 +3994,11 @@
       </c>
       <c r="G61" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="H61" s="46" t="n">
-        <v>2680000</v>
+        <v>2380000</v>
       </c>
       <c r="I61" s="27" t="inlineStr"/>
       <c r="J61" s="27" t="inlineStr">
@@ -4029,7 +4021,7 @@
     <row r="62">
       <c r="A62" s="36" t="inlineStr">
         <is>
-          <t>DEV-00439</t>
+          <t>DEV-00438</t>
         </is>
       </c>
       <c r="B62" s="27" t="inlineStr">
@@ -4059,11 +4051,11 @@
       </c>
       <c r="G62" s="27" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="H62" s="46" t="n">
-        <v>1240000</v>
+        <v>2680000</v>
       </c>
       <c r="I62" s="27" t="inlineStr"/>
       <c r="J62" s="27" t="inlineStr">
@@ -4086,7 +4078,7 @@
     <row r="63">
       <c r="A63" s="36" t="inlineStr">
         <is>
-          <t>DEV-00440</t>
+          <t>DEV-00439</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
@@ -4106,7 +4098,7 @@
       </c>
       <c r="E63" s="27" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F63" s="27" t="inlineStr">
@@ -4116,16 +4108,16 @@
       </c>
       <c r="G63" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="H63" s="46" t="n">
-        <v>6760</v>
+        <v>1240000</v>
       </c>
       <c r="I63" s="27" t="inlineStr"/>
       <c r="J63" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K63" s="27" t="inlineStr">
@@ -4143,7 +4135,7 @@
     <row r="64">
       <c r="A64" s="36" t="inlineStr">
         <is>
-          <t>DEV-00441</t>
+          <t>DEV-00440</t>
         </is>
       </c>
       <c r="B64" s="27" t="inlineStr">
@@ -4173,16 +4165,16 @@
       </c>
       <c r="G64" s="27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H64" s="46" t="n">
-        <v>2330000</v>
+        <v>6760</v>
       </c>
       <c r="I64" s="27" t="inlineStr"/>
       <c r="J64" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K64" s="27" t="inlineStr">
@@ -4200,7 +4192,7 @@
     <row r="65">
       <c r="A65" s="36" t="inlineStr">
         <is>
-          <t>DEV-00442</t>
+          <t>DEV-00441</t>
         </is>
       </c>
       <c r="B65" s="27" t="inlineStr">
@@ -4230,11 +4222,11 @@
       </c>
       <c r="G65" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="H65" s="46" t="n">
-        <v>2720000</v>
+        <v>2330000</v>
       </c>
       <c r="I65" s="27" t="inlineStr"/>
       <c r="J65" s="27" t="inlineStr">
@@ -4257,7 +4249,7 @@
     <row r="66">
       <c r="A66" s="36" t="inlineStr">
         <is>
-          <t>DEV-00443</t>
+          <t>DEV-00442</t>
         </is>
       </c>
       <c r="B66" s="27" t="inlineStr">
@@ -4287,11 +4279,11 @@
       </c>
       <c r="G66" s="27" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="H66" s="46" t="n">
-        <v>1290000</v>
+        <v>2720000</v>
       </c>
       <c r="I66" s="27" t="inlineStr"/>
       <c r="J66" s="27" t="inlineStr">
@@ -4314,7 +4306,7 @@
     <row r="67">
       <c r="A67" s="36" t="inlineStr">
         <is>
-          <t>DEV-00444</t>
+          <t>DEV-00443</t>
         </is>
       </c>
       <c r="B67" s="27" t="inlineStr">
@@ -4334,7 +4326,7 @@
       </c>
       <c r="E67" s="27" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F67" s="27" t="inlineStr">
@@ -4344,16 +4336,16 @@
       </c>
       <c r="G67" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="H67" s="46" t="n">
-        <v>7050</v>
+        <v>1290000</v>
       </c>
       <c r="I67" s="27" t="inlineStr"/>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K67" s="27" t="inlineStr">
@@ -4371,7 +4363,7 @@
     <row r="68">
       <c r="A68" s="36" t="inlineStr">
         <is>
-          <t>DEV-00445</t>
+          <t>DEV-00444</t>
         </is>
       </c>
       <c r="B68" s="27" t="inlineStr">
@@ -4401,16 +4393,16 @@
       </c>
       <c r="G68" s="27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H68" s="46" t="n">
-        <v>2490000</v>
+        <v>7050</v>
       </c>
       <c r="I68" s="27" t="inlineStr"/>
       <c r="J68" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K68" s="27" t="inlineStr">
@@ -4428,7 +4420,7 @@
     <row r="69">
       <c r="A69" s="36" t="inlineStr">
         <is>
-          <t>DEV-00446</t>
+          <t>DEV-00445</t>
         </is>
       </c>
       <c r="B69" s="27" t="inlineStr">
@@ -4458,11 +4450,11 @@
       </c>
       <c r="G69" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="H69" s="46" t="n">
-        <v>2820000</v>
+        <v>2490000</v>
       </c>
       <c r="I69" s="27" t="inlineStr"/>
       <c r="J69" s="27" t="inlineStr">
@@ -4485,7 +4477,7 @@
     <row r="70">
       <c r="A70" s="36" t="inlineStr">
         <is>
-          <t>DEV-00447</t>
+          <t>DEV-00446</t>
         </is>
       </c>
       <c r="B70" s="27" t="inlineStr">
@@ -4515,11 +4507,11 @@
       </c>
       <c r="G70" s="27" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="H70" s="46" t="n">
-        <v>1330000</v>
+        <v>2820000</v>
       </c>
       <c r="I70" s="27" t="inlineStr"/>
       <c r="J70" s="27" t="inlineStr">
@@ -4542,7 +4534,7 @@
     <row r="71">
       <c r="A71" s="36" t="inlineStr">
         <is>
-          <t>DEV-00448</t>
+          <t>DEV-00447</t>
         </is>
       </c>
       <c r="B71" s="27" t="inlineStr">
@@ -4562,7 +4554,7 @@
       </c>
       <c r="E71" s="27" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F71" s="27" t="inlineStr">
@@ -4572,16 +4564,16 @@
       </c>
       <c r="G71" s="27" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="H71" s="46" t="n">
-        <v>7320</v>
+        <v>1330000</v>
       </c>
       <c r="I71" s="27" t="inlineStr"/>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K71" s="27" t="inlineStr">
@@ -4599,7 +4591,7 @@
     <row r="72">
       <c r="A72" s="36" t="inlineStr">
         <is>
-          <t>DEV-00449</t>
+          <t>DEV-00448</t>
         </is>
       </c>
       <c r="B72" s="27" t="inlineStr">
@@ -4629,16 +4621,16 @@
       </c>
       <c r="G72" s="27" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="H72" s="46" t="n">
-        <v>2630000</v>
+        <v>7320</v>
       </c>
       <c r="I72" s="27" t="inlineStr"/>
       <c r="J72" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K72" s="27" t="inlineStr">
@@ -4656,7 +4648,7 @@
     <row r="73">
       <c r="A73" s="36" t="inlineStr">
         <is>
-          <t>DEV-00450</t>
+          <t>DEV-00449</t>
         </is>
       </c>
       <c r="B73" s="27" t="inlineStr">
@@ -4686,11 +4678,11 @@
       </c>
       <c r="G73" s="27" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="H73" s="46" t="n">
-        <v>2910000</v>
+        <v>2630000</v>
       </c>
       <c r="I73" s="27" t="inlineStr"/>
       <c r="J73" s="27" t="inlineStr">
@@ -4713,7 +4705,7 @@
     <row r="74">
       <c r="A74" s="36" t="inlineStr">
         <is>
-          <t>DEV-00451</t>
+          <t>DEV-00450</t>
         </is>
       </c>
       <c r="B74" s="27" t="inlineStr">
@@ -4743,11 +4735,11 @@
       </c>
       <c r="G74" s="27" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="H74" s="46" t="n">
-        <v>1360000</v>
+        <v>2910000</v>
       </c>
       <c r="I74" s="27" t="inlineStr"/>
       <c r="J74" s="27" t="inlineStr">
@@ -4770,7 +4762,7 @@
     <row r="75">
       <c r="A75" s="36" t="inlineStr">
         <is>
-          <t>DEV-00452</t>
+          <t>DEV-00451</t>
         </is>
       </c>
       <c r="B75" s="27" t="inlineStr">
@@ -4780,7 +4772,7 @@
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>Purchase price terms</t>
+          <t>Target monthly working capital</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -4790,7 +4782,7 @@
       </c>
       <c r="E75" s="27" t="inlineStr">
         <is>
-          <t>Signing</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F75" s="27" t="inlineStr">
@@ -4800,16 +4792,16 @@
       </c>
       <c r="G75" s="27" t="inlineStr">
         <is>
-          <t>Equity purchase price</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="H75" s="46" t="n">
-        <v>31500</v>
+        <v>1360000</v>
       </c>
       <c r="I75" s="27" t="inlineStr"/>
       <c r="J75" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K75" s="27" t="inlineStr">
@@ -4827,7 +4819,7 @@
     <row r="76">
       <c r="A76" s="36" t="inlineStr">
         <is>
-          <t>DEV-00453</t>
+          <t>DEV-00452</t>
         </is>
       </c>
       <c r="B76" s="27" t="inlineStr">
@@ -4857,16 +4849,16 @@
       </c>
       <c r="G76" s="27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Equity purchase price</t>
         </is>
       </c>
       <c r="H76" s="46" t="n">
-        <v>1250000</v>
+        <v>31500</v>
       </c>
       <c r="I76" s="27" t="inlineStr"/>
       <c r="J76" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K76" s="27" t="inlineStr">
@@ -4884,7 +4876,7 @@
     <row r="77">
       <c r="A77" s="36" t="inlineStr">
         <is>
-          <t>DEV-00454</t>
+          <t>DEV-00453</t>
         </is>
       </c>
       <c r="B77" s="27" t="inlineStr">
@@ -4914,11 +4906,11 @@
       </c>
       <c r="G77" s="27" t="inlineStr">
         <is>
-          <t>Funded debt</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="H77" s="46" t="n">
-        <v>4700000</v>
+        <v>1250000</v>
       </c>
       <c r="I77" s="27" t="inlineStr"/>
       <c r="J77" s="27" t="inlineStr">
@@ -4941,7 +4933,7 @@
     <row r="78">
       <c r="A78" s="36" t="inlineStr">
         <is>
-          <t>DEV-00455</t>
+          <t>DEV-00454</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
@@ -4971,11 +4963,11 @@
       </c>
       <c r="G78" s="27" t="inlineStr">
         <is>
-          <t>Debt-like transaction bonus</t>
+          <t>Funded debt</t>
         </is>
       </c>
       <c r="H78" s="46" t="n">
-        <v>620000</v>
+        <v>4700000</v>
       </c>
       <c r="I78" s="27" t="inlineStr"/>
       <c r="J78" s="27" t="inlineStr">
@@ -4998,7 +4990,7 @@
     <row r="79">
       <c r="A79" s="36" t="inlineStr">
         <is>
-          <t>DEV-00456</t>
+          <t>DEV-00455</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
@@ -5028,16 +5020,16 @@
       </c>
       <c r="G79" s="27" t="inlineStr">
         <is>
-          <t>Debt-like deferred payroll tax</t>
+          <t>Debt-like transaction bonus</t>
         </is>
       </c>
       <c r="H79" s="46" t="n">
-        <v>310</v>
+        <v>620000</v>
       </c>
       <c r="I79" s="27" t="inlineStr"/>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>USD thousands</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K79" s="27" t="inlineStr">
@@ -5055,7 +5047,7 @@
     <row r="80">
       <c r="A80" s="36" t="inlineStr">
         <is>
-          <t>DEV-00457</t>
+          <t>DEV-00456</t>
         </is>
       </c>
       <c r="B80" s="27" t="inlineStr">
@@ -5085,16 +5077,16 @@
       </c>
       <c r="G80" s="27" t="inlineStr">
         <is>
-          <t>Seller retained tax receivable</t>
+          <t>Debt-like deferred payroll tax</t>
         </is>
       </c>
       <c r="H80" s="46" t="n">
-        <v>240000</v>
+        <v>310</v>
       </c>
       <c r="I80" s="27" t="inlineStr"/>
       <c r="J80" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD thousands</t>
         </is>
       </c>
       <c r="K80" s="27" t="inlineStr">
@@ -5112,7 +5104,7 @@
     <row r="81">
       <c r="A81" s="36" t="inlineStr">
         <is>
-          <t>DEV-00458</t>
+          <t>DEV-00457</t>
         </is>
       </c>
       <c r="B81" s="27" t="inlineStr">
@@ -5142,11 +5134,11 @@
       </c>
       <c r="G81" s="27" t="inlineStr">
         <is>
-          <t>Minimum cash delivered</t>
+          <t>Seller retained tax receivable</t>
         </is>
       </c>
       <c r="H81" s="46" t="n">
-        <v>750000</v>
+        <v>240000</v>
       </c>
       <c r="I81" s="27" t="inlineStr"/>
       <c r="J81" s="27" t="inlineStr">
@@ -5169,7 +5161,7 @@
     <row r="82">
       <c r="A82" s="36" t="inlineStr">
         <is>
-          <t>DEV-00459</t>
+          <t>DEV-00458</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
@@ -5199,16 +5191,16 @@
       </c>
       <c r="G82" s="27" t="inlineStr">
         <is>
-          <t>NWC peg lookback months</t>
+          <t>Minimum cash delivered</t>
         </is>
       </c>
       <c r="H82" s="46" t="n">
-        <v>6</v>
+        <v>750000</v>
       </c>
       <c r="I82" s="27" t="inlineStr"/>
       <c r="J82" s="27" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K82" s="27" t="inlineStr">
@@ -5226,7 +5218,7 @@
     <row r="83">
       <c r="A83" s="36" t="inlineStr">
         <is>
-          <t>DEV-00476</t>
+          <t>DEV-00459</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
@@ -5236,17 +5228,17 @@
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>Locked box leakage review</t>
+          <t>Purchase price terms</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Owner dividend</t>
+          <t>Pioneer HVAC</t>
         </is>
       </c>
       <c r="E83" s="27" t="inlineStr">
         <is>
-          <t>Signing to close</t>
+          <t>Signing</t>
         </is>
       </c>
       <c r="F83" s="27" t="inlineStr">
@@ -5256,16 +5248,16 @@
       </c>
       <c r="G83" s="27" t="inlineStr">
         <is>
-          <t>Cash outflow</t>
+          <t>NWC peg lookback months</t>
         </is>
       </c>
       <c r="H83" s="46" t="n">
-        <v>310000</v>
+        <v>6</v>
       </c>
       <c r="I83" s="27" t="inlineStr"/>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>count</t>
         </is>
       </c>
       <c r="K83" s="27" t="inlineStr">
@@ -5283,7 +5275,7 @@
     <row r="84">
       <c r="A84" s="36" t="inlineStr">
         <is>
-          <t>DEV-00477</t>
+          <t>DEV-00476</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
@@ -5313,16 +5305,16 @@
       </c>
       <c r="G84" s="27" t="inlineStr">
         <is>
-          <t>Permitted leakage</t>
+          <t>Cash outflow</t>
         </is>
       </c>
       <c r="H84" s="46" t="n">
-        <v>0</v>
+        <v>310000</v>
       </c>
       <c r="I84" s="27" t="inlineStr"/>
       <c r="J84" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K84" s="27" t="inlineStr">
@@ -5340,7 +5332,7 @@
     <row r="85">
       <c r="A85" s="36" t="inlineStr">
         <is>
-          <t>DEV-00478</t>
+          <t>DEV-00477</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
@@ -5355,7 +5347,7 @@
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Tax distribution</t>
+          <t>Owner dividend</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
@@ -5370,16 +5362,16 @@
       </c>
       <c r="G85" s="27" t="inlineStr">
         <is>
-          <t>Cash outflow</t>
+          <t>Permitted leakage</t>
         </is>
       </c>
       <c r="H85" s="46" t="n">
-        <v>185000</v>
+        <v>0</v>
       </c>
       <c r="I85" s="27" t="inlineStr"/>
       <c r="J85" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K85" s="27" t="inlineStr">
@@ -5397,7 +5389,7 @@
     <row r="86">
       <c r="A86" s="36" t="inlineStr">
         <is>
-          <t>DEV-00479</t>
+          <t>DEV-00478</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
@@ -5427,16 +5419,16 @@
       </c>
       <c r="G86" s="27" t="inlineStr">
         <is>
-          <t>Permitted leakage</t>
+          <t>Cash outflow</t>
         </is>
       </c>
       <c r="H86" s="46" t="n">
-        <v>1</v>
+        <v>185000</v>
       </c>
       <c r="I86" s="27" t="inlineStr"/>
       <c r="J86" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K86" s="27" t="inlineStr">
@@ -5454,7 +5446,7 @@
     <row r="87">
       <c r="A87" s="36" t="inlineStr">
         <is>
-          <t>DEV-00480</t>
+          <t>DEV-00479</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
@@ -5469,7 +5461,7 @@
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>Related-party consulting</t>
+          <t>Tax distribution</t>
         </is>
       </c>
       <c r="E87" s="27" t="inlineStr">
@@ -5484,16 +5476,16 @@
       </c>
       <c r="G87" s="27" t="inlineStr">
         <is>
-          <t>Cash outflow</t>
+          <t>Permitted leakage</t>
         </is>
       </c>
       <c r="H87" s="46" t="n">
-        <v>140000</v>
+        <v>1</v>
       </c>
       <c r="I87" s="27" t="inlineStr"/>
       <c r="J87" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K87" s="27" t="inlineStr">
@@ -5511,7 +5503,7 @@
     <row r="88">
       <c r="A88" s="36" t="inlineStr">
         <is>
-          <t>DEV-00481</t>
+          <t>DEV-00480</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
@@ -5541,16 +5533,16 @@
       </c>
       <c r="G88" s="27" t="inlineStr">
         <is>
-          <t>Permitted leakage</t>
+          <t>Cash outflow</t>
         </is>
       </c>
       <c r="H88" s="46" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="I88" s="27" t="inlineStr"/>
       <c r="J88" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K88" s="27" t="inlineStr">
@@ -5568,7 +5560,7 @@
     <row r="89">
       <c r="A89" s="36" t="inlineStr">
         <is>
-          <t>DEV-00482</t>
+          <t>DEV-00481</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
@@ -5583,7 +5575,7 @@
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Ordinary payroll</t>
+          <t>Related-party consulting</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
@@ -5598,16 +5590,16 @@
       </c>
       <c r="G89" s="27" t="inlineStr">
         <is>
-          <t>Cash outflow</t>
+          <t>Permitted leakage</t>
         </is>
       </c>
       <c r="H89" s="46" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="I89" s="27" t="inlineStr"/>
       <c r="J89" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K89" s="27" t="inlineStr">
@@ -5625,7 +5617,7 @@
     <row r="90">
       <c r="A90" s="36" t="inlineStr">
         <is>
-          <t>DEV-00483</t>
+          <t>DEV-00482</t>
         </is>
       </c>
       <c r="B90" s="27" t="inlineStr">
@@ -5655,16 +5647,16 @@
       </c>
       <c r="G90" s="27" t="inlineStr">
         <is>
-          <t>Permitted leakage</t>
+          <t>Cash outflow</t>
         </is>
       </c>
       <c r="H90" s="46" t="n">
-        <v>1</v>
+        <v>95000</v>
       </c>
       <c r="I90" s="27" t="inlineStr"/>
       <c r="J90" s="27" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K90" s="27" t="inlineStr">
@@ -5682,7 +5674,7 @@
     <row r="91">
       <c r="A91" s="36" t="inlineStr">
         <is>
-          <t>DEV-00484</t>
+          <t>DEV-00483</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
@@ -5692,17 +5684,17 @@
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>Closing funds flow terms</t>
+          <t>Locked box leakage review</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Pioneer HVAC</t>
+          <t>Ordinary payroll</t>
         </is>
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Signing to close</t>
         </is>
       </c>
       <c r="F91" s="27" t="inlineStr">
@@ -5712,16 +5704,16 @@
       </c>
       <c r="G91" s="27" t="inlineStr">
         <is>
-          <t>Escrow percent of adjusted equity price</t>
+          <t>Permitted leakage</t>
         </is>
       </c>
       <c r="H91" s="46" t="n">
-        <v>0.075</v>
+        <v>1</v>
       </c>
       <c r="I91" s="27" t="inlineStr"/>
       <c r="J91" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="K91" s="27" t="inlineStr">
@@ -5739,7 +5731,7 @@
     <row r="92">
       <c r="A92" s="36" t="inlineStr">
         <is>
-          <t>DEV-00485</t>
+          <t>DEV-00484</t>
         </is>
       </c>
       <c r="B92" s="27" t="inlineStr">
@@ -5769,16 +5761,16 @@
       </c>
       <c r="G92" s="27" t="inlineStr">
         <is>
-          <t>Earnout face value</t>
+          <t>Escrow percent of adjusted equity price</t>
         </is>
       </c>
       <c r="H92" s="46" t="n">
-        <v>4500000</v>
+        <v>0.075</v>
       </c>
       <c r="I92" s="27" t="inlineStr"/>
       <c r="J92" s="27" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>decimal ratio</t>
         </is>
       </c>
       <c r="K92" s="27" t="inlineStr">
@@ -5796,7 +5788,7 @@
     <row r="93">
       <c r="A93" s="36" t="inlineStr">
         <is>
-          <t>DEV-00486</t>
+          <t>DEV-00485</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
@@ -5826,16 +5818,16 @@
       </c>
       <c r="G93" s="27" t="inlineStr">
         <is>
-          <t>Earnout probability</t>
+          <t>Earnout face value</t>
         </is>
       </c>
       <c r="H93" s="46" t="n">
-        <v>0.55</v>
+        <v>4500000</v>
       </c>
       <c r="I93" s="27" t="inlineStr"/>
       <c r="J93" s="27" t="inlineStr">
         <is>
-          <t>decimal ratio</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K93" s="27" t="inlineStr">
@@ -5853,7 +5845,7 @@
     <row r="94">
       <c r="A94" s="36" t="inlineStr">
         <is>
-          <t>DEV-00487</t>
+          <t>DEV-00486</t>
         </is>
       </c>
       <c r="B94" s="27" t="inlineStr">
@@ -5883,11 +5875,11 @@
       </c>
       <c r="G94" s="27" t="inlineStr">
         <is>
-          <t>Earnout discount factor</t>
+          <t>Earnout probability</t>
         </is>
       </c>
       <c r="H94" s="46" t="n">
-        <v>0.89</v>
+        <v>0.55</v>
       </c>
       <c r="I94" s="27" t="inlineStr"/>
       <c r="J94" s="27" t="inlineStr">
@@ -5910,7 +5902,7 @@
     <row r="95">
       <c r="A95" s="36" t="inlineStr">
         <is>
-          <t>DEV-00488</t>
+          <t>DEV-00487</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
@@ -5940,32 +5932,89 @@
       </c>
       <c r="G95" s="27" t="inlineStr">
         <is>
-          <t>Transaction expenses paid at close</t>
+          <t>Earnout discount factor</t>
         </is>
       </c>
       <c r="H95" s="46" t="n">
-        <v>780000</v>
+        <v>0.89</v>
       </c>
       <c r="I95" s="27" t="inlineStr"/>
       <c r="J95" s="27" t="inlineStr">
         <is>
+          <t>decimal ratio</t>
+        </is>
+      </c>
+      <c r="K95" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L95" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M95" s="27" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="36" t="inlineStr">
+        <is>
+          <t>DEV-00488</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>Create the Pioneer QoE and purchase-price bridge</t>
+        </is>
+      </c>
+      <c r="C96" s="27" t="inlineStr">
+        <is>
+          <t>Closing funds flow terms</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>Pioneer HVAC</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="F96" s="27" t="inlineStr">
+        <is>
+          <t>Approved case</t>
+        </is>
+      </c>
+      <c r="G96" s="27" t="inlineStr">
+        <is>
+          <t>Transaction expenses paid at close</t>
+        </is>
+      </c>
+      <c r="H96" s="46" t="n">
+        <v>780000</v>
+      </c>
+      <c r="I96" s="27" t="inlineStr"/>
+      <c r="J96" s="27" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="K95" s="27" t="inlineStr">
-        <is>
-          <t>Finance operating schedule</t>
-        </is>
-      </c>
-      <c r="L95" s="47" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="M95" s="27" t="inlineStr"/>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Finance operating schedule</t>
+        </is>
+      </c>
+      <c r="L96" s="47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="M96" s="27" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M95"/>
+  <autoFilter ref="A4:M96"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -25392,10 +25441,10 @@
         </is>
       </c>
       <c r="B5" s="40" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" s="40">
-        <f>COUNTA('QoE and Working Capital'!$A$5:$A$95)</f>
+        <f>COUNTA('QoE and Working Capital'!$A$5:$A$96)</f>
         <v/>
       </c>
       <c r="D5" s="40">
@@ -25446,10 +25495,10 @@
         </is>
       </c>
       <c r="B7" s="41" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C7" s="41">
-        <f>COUNTA('Transaction Models'!$A$5:$A$205)</f>
+        <f>COUNTA('Transaction Models'!$A$5:$A$206)</f>
         <v/>
       </c>
       <c r="D7" s="41">
